--- a/framework-templates/Document_Log_Pricing_v2.0.xlsx
+++ b/framework-templates/Document_Log_Pricing_v2.0.xlsx
@@ -58,7 +58,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -69,11 +69,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,7 +116,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,19 +164,16 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1042,7 +1034,7 @@
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
-          <t>Compliance Monitoring Pack; Customer Due Diligence Pack; Consumer Duty Pack; Financial Promotions Pack</t>
+          <t>Compliance Monitoring Pack; Customer Due Diligence Pack; Consumer Duty Pack</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1081,7 @@
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>AML Pack; Compliance Monitoring Pack; Risk Management Pack; Training Pack; Data Protection Pack</t>
+          <t>AML Pack; Compliance Monitoring Pack; Risk Management Pack; Training Pack</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1220,7 @@
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
-          <t>Training Pack; Financial Promotions Pack</t>
+          <t>Training Pack; Consumer Duty Pack</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1360,16 @@
     <row r="22">
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Customer Due Diligence Policy</t>
+          <t>Data Processing Policy</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>Customer Due Diligence Pack</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>https://buy.stripe.com/28E4gs9xb4pv6OdeGDfbq00</t>
-        </is>
-      </c>
+          <t>Compliance Monitoring Pack</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
       <c r="F22" s="13" t="n"/>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -1409,7 +1395,7 @@
       </c>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>Customer_Due_Diligence_Policy_v2.0_Template.docx</t>
+          <t>Data_Processing_Policy_v2.0_Template.docx</t>
         </is>
       </c>
       <c r="N22" s="13" t="n"/>
@@ -1417,12 +1403,12 @@
     <row r="23">
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Customer Vulnerability Policy</t>
+          <t>Record of Processing Activities</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>Customer Due Diligence Pack</t>
+          <t>Compliance Monitoring Pack</t>
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
@@ -1447,25 +1433,29 @@
       </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
-          <t>Policy.</t>
+          <t>Register.</t>
         </is>
       </c>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>Customer_Vulnerability_Policy_v2.0_Template.docx</t>
-        </is>
-      </c>
-      <c r="N23" s="13" t="n"/>
+          <t>Record_of_Processing_Activities_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>Customer Due Diligence Pack</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>Customer Due Diligence Checklist</t>
+          <t>Data Rights Request Log</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>Customer Due Diligence Pack</t>
+          <t>Compliance Monitoring Pack</t>
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
@@ -1495,24 +1485,20 @@
       </c>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t>Customer_Due_Diligence_Checklist_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N24" s="13" t="inlineStr">
-        <is>
-          <t>AML Pack</t>
-        </is>
-      </c>
+          <t>Data_Rights_Request_Log_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N24" s="13" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Enhanced Due Diligence Checklist</t>
+          <t>Data Breach Log</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>Customer Due Diligence Pack</t>
+          <t>Compliance Monitoring Pack</t>
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
@@ -1542,24 +1528,20 @@
       </c>
       <c r="M25" s="13" t="inlineStr">
         <is>
-          <t>Enhanced_Due_Diligence_Checklist_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N25" s="13" t="inlineStr">
-        <is>
-          <t>AML Pack</t>
-        </is>
-      </c>
+          <t>Data_Breach_Log_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N25" s="13" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>Customer Due Diligence Register</t>
+          <t>Data Protection Complaints Log</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>Customer Due Diligence Pack</t>
+          <t>Compliance Monitoring Pack</t>
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
@@ -1589,34 +1571,28 @@
       </c>
       <c r="M26" s="13" t="inlineStr">
         <is>
-          <t>Customer_Due_Diligence_Register_v2.0_Template.xlsx</t>
+          <t>Data_Protection_Complaints_Log_v2.0_Template.xlsx</t>
         </is>
       </c>
       <c r="N26" s="13" t="inlineStr">
         <is>
-          <t>AML Pack; Compliance Monitoring Pack</t>
+          <t>Complaints Pack</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>SM&amp;CR Statement of Responsibilities</t>
+          <t>Data Retention Schedule</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Senior Management Pack</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>35</v>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>https://buy.stripe.com/4gMdR238NbRX2xXcyvfbq04</t>
-        </is>
-      </c>
+          <t>Compliance Monitoring Pack</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
       <c r="F27" s="13" t="n"/>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -1637,12 +1613,12 @@
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
-          <t>Policy.</t>
+          <t>Register.</t>
         </is>
       </c>
       <c r="M27" s="13" t="inlineStr">
         <is>
-          <t>SMCR_Statement_of_Responsibilities_v2.0_Template.docx</t>
+          <t>Data_Retention_Schedule_v2.0_Template.xlsx</t>
         </is>
       </c>
       <c r="N27" s="13" t="n"/>
@@ -1650,12 +1626,12 @@
     <row r="28">
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>FIT and Proper Questionnaire</t>
+          <t>DPIA Register</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Senior Management Pack</t>
+          <t>Compliance Monitoring Pack</t>
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
@@ -1663,21 +1639,29 @@
       <c r="F28" s="13" t="n"/>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H28" s="13" t="n"/>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>KMS Compliance (AI-assisted v2.0 rewrite)</t>
+        </is>
+      </c>
       <c r="I28" s="13" t="n"/>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
+      <c r="J28" s="16" t="n">
+        <v>46290</v>
+      </c>
+      <c r="K28" s="16" t="n">
+        <v>46655</v>
+      </c>
       <c r="L28" s="13" t="inlineStr">
         <is>
-          <t>Form. Not updated in the v2.0 rewrite – review separately.</t>
+          <t>Register.</t>
         </is>
       </c>
       <c r="M28" s="13" t="inlineStr">
         <is>
-          <t>FIT_and_Proper_Questionnaire_v1.0.docx</t>
+          <t>DPIA_Register_v2.0_Template.xlsx</t>
         </is>
       </c>
       <c r="N28" s="13" t="n"/>
@@ -1685,20 +1669,20 @@
     <row r="29">
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Consumer Duty Implementation and Embedding Plan</t>
+          <t>Customer Due Diligence Policy</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Consumer Duty Pack</t>
+          <t>Customer Due Diligence Pack</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>https://buy.stripe.com/28E28kbFj1djb4t41Zfbq06</t>
+          <t>https://buy.stripe.com/28E4gs9xb4pv6OdeGDfbq00</t>
         </is>
       </c>
       <c r="F29" s="13" t="n"/>
@@ -1726,7 +1710,7 @@
       </c>
       <c r="M29" s="13" t="inlineStr">
         <is>
-          <t>Consumer_Duty_Implementation_Plan_v2.0_Template.docx</t>
+          <t>Customer_Due_Diligence_Policy_v2.0_Template.docx</t>
         </is>
       </c>
       <c r="N29" s="13" t="n"/>
@@ -1734,12 +1718,12 @@
     <row r="30">
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Consumer Duty Outcome MI</t>
+          <t>Customer Vulnerability Policy</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Consumer Duty Pack</t>
+          <t>Customer Due Diligence Pack</t>
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
@@ -1764,29 +1748,25 @@
       </c>
       <c r="L30" s="13" t="inlineStr">
         <is>
-          <t>Register.</t>
+          <t>Policy.</t>
         </is>
       </c>
       <c r="M30" s="13" t="inlineStr">
         <is>
-          <t>Consumer_Duty_Outcome_MI_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N30" s="13" t="inlineStr">
-        <is>
-          <t>Complaints Pack; Compliance Monitoring Pack; Customer Due Diligence Pack; Risk Management Pack</t>
-        </is>
-      </c>
+          <t>Customer_Vulnerability_Policy_v2.0_Template.docx</t>
+        </is>
+      </c>
+      <c r="N30" s="13" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Target Market Register</t>
+          <t>Customer Due Diligence Checklist</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Consumer Duty Pack</t>
+          <t>Customer Due Diligence Pack</t>
         </is>
       </c>
       <c r="D31" s="13" t="n"/>
@@ -1816,20 +1796,24 @@
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>Target_Market_Register_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N31" s="13" t="n"/>
+          <t>Customer_Due_Diligence_Checklist_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N31" s="13" t="inlineStr">
+        <is>
+          <t>AML Pack</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>Fair Value Register</t>
+          <t>Enhanced Due Diligence Checklist</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>Consumer Duty Pack</t>
+          <t>Customer Due Diligence Pack</t>
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
@@ -1859,20 +1843,24 @@
       </c>
       <c r="M32" s="13" t="inlineStr">
         <is>
-          <t>Fair_Value_Register_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N32" s="13" t="n"/>
+          <t>Enhanced_Due_Diligence_Checklist_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N32" s="13" t="inlineStr">
+        <is>
+          <t>AML Pack</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Consumer Duty Board Report Actions</t>
+          <t>Customer Due Diligence Register</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>Consumer Duty Pack</t>
+          <t>Customer Due Diligence Pack</t>
         </is>
       </c>
       <c r="D33" s="13" t="n"/>
@@ -1902,20 +1890,24 @@
       </c>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>Consumer_Duty_Board_Report_Actions_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N33" s="13" t="n"/>
+          <t>Customer_Due_Diligence_Register_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N33" s="13" t="inlineStr">
+        <is>
+          <t>AML Pack; Compliance Monitoring Pack</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Risk Management Framework</t>
+          <t>SM&amp;CR Statement of Responsibilities</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>Risk Management Pack</t>
+          <t>Senior Management Pack</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
@@ -1923,7 +1915,7 @@
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>https://buy.stripe.com/7sY14g9xb5tz8Wl41Zfbq07</t>
+          <t>https://buy.stripe.com/4gMdR238NbRX2xXcyvfbq04</t>
         </is>
       </c>
       <c r="F34" s="13" t="n"/>
@@ -1951,7 +1943,7 @@
       </c>
       <c r="M34" s="13" t="inlineStr">
         <is>
-          <t>Risk_Management_Framework_v2.0_Template.docx</t>
+          <t>SMCR_Statement_of_Responsibilities_v2.0_Template.docx</t>
         </is>
       </c>
       <c r="N34" s="13" t="n"/>
@@ -1959,12 +1951,12 @@
     <row r="35">
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Risk Assessment Log</t>
+          <t>FIT and Proper Questionnaire</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>Risk Management Pack</t>
+          <t>Senior Management Pack</t>
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
@@ -1972,46 +1964,34 @@
       <c r="F35" s="13" t="n"/>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="H35" s="13" t="inlineStr">
-        <is>
-          <t>KMS Compliance (AI-assisted v2.0 rewrite)</t>
-        </is>
-      </c>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="n"/>
       <c r="I35" s="13" t="n"/>
-      <c r="J35" s="16" t="n">
-        <v>46290</v>
-      </c>
-      <c r="K35" s="16" t="n">
-        <v>46655</v>
-      </c>
+      <c r="J35" s="16" t="n"/>
+      <c r="K35" s="16" t="n"/>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>Register.</t>
+          <t>Form. Not updated in the v2.0 rewrite – review separately.</t>
         </is>
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>Risk_Assessment_Log_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N35" s="13" t="inlineStr">
-        <is>
-          <t>Compliance Monitoring Pack; Consumer Duty Pack</t>
-        </is>
-      </c>
+          <t>FIT_and_Proper_Questionnaire_v1.0.docx</t>
+        </is>
+      </c>
+      <c r="N35" s="13" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Training and Competence Policy</t>
+          <t>Consumer Duty Implementation and Embedding Plan</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>Training Pack</t>
+          <t>Consumer Duty Pack</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
@@ -2019,7 +1999,7 @@
       </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
-          <t>https://buy.stripe.com/eVq28kaBf09fa0p6a7fbq08</t>
+          <t>https://buy.stripe.com/28E28kbFj1djb4t41Zfbq06</t>
         </is>
       </c>
       <c r="F36" s="13" t="n"/>
@@ -2047,7 +2027,7 @@
       </c>
       <c r="M36" s="13" t="inlineStr">
         <is>
-          <t>Training_and_Competence_Policy_v2.0_Template.docx</t>
+          <t>Consumer_Duty_Implementation_Plan_v2.0_Template.docx</t>
         </is>
       </c>
       <c r="N36" s="13" t="n"/>
@@ -2055,12 +2035,12 @@
     <row r="37">
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Training Matrix</t>
+          <t>Consumer Duty Outcome MI</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>Training Pack</t>
+          <t>Consumer Duty Pack</t>
         </is>
       </c>
       <c r="D37" s="13" t="n"/>
@@ -2090,20 +2070,24 @@
       </c>
       <c r="M37" s="13" t="inlineStr">
         <is>
-          <t>Training_Matrix_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N37" s="13" t="n"/>
+          <t>Consumer_Duty_Outcome_MI_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N37" s="13" t="inlineStr">
+        <is>
+          <t>Complaints Pack; Compliance Monitoring Pack; Customer Due Diligence Pack; Risk Management Pack</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Training Log</t>
+          <t>Target Market Register</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>Training Pack</t>
+          <t>Consumer Duty Pack</t>
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
@@ -2133,24 +2117,20 @@
       </c>
       <c r="M38" s="13" t="inlineStr">
         <is>
-          <t>Training_Log_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N38" s="13" t="inlineStr">
-        <is>
-          <t>All other packs</t>
-        </is>
-      </c>
+          <t>Target_Market_Register_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N38" s="13" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>Competence Register</t>
+          <t>Fair Value Register</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>Training Pack</t>
+          <t>Consumer Duty Pack</t>
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
@@ -2180,24 +2160,20 @@
       </c>
       <c r="M39" s="13" t="inlineStr">
         <is>
-          <t>Competence_Register_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N39" s="13" t="inlineStr">
-        <is>
-          <t>Compliance Monitoring Pack; Senior Management Pack</t>
-        </is>
-      </c>
+          <t>Fair_Value_Register_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N39" s="13" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>CPD Log</t>
+          <t>Consumer Duty Board Report Actions</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>Training Pack</t>
+          <t>Consumer Duty Pack</t>
         </is>
       </c>
       <c r="D40" s="13" t="n"/>
@@ -2227,7 +2203,7 @@
       </c>
       <c r="M40" s="13" t="inlineStr">
         <is>
-          <t>CPD_Log_v2.0_Template.xlsx</t>
+          <t>Consumer_Duty_Board_Report_Actions_v2.0_Template.xlsx</t>
         </is>
       </c>
       <c r="N40" s="13" t="n"/>
@@ -2235,12 +2211,12 @@
     <row r="41">
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>Individual Training Record (optional)</t>
+          <t>Financial Promotions Policy</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>Training Pack</t>
+          <t>Consumer Duty Pack</t>
         </is>
       </c>
       <c r="D41" s="13" t="n"/>
@@ -2265,12 +2241,12 @@
       </c>
       <c r="L41" s="13" t="inlineStr">
         <is>
-          <t>Register.</t>
+          <t>Policy.</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr">
         <is>
-          <t>Individual_Training_Record_v2.0_Template.xlsx</t>
+          <t>Financial_Promotions_Policy_v2.0_Template.docx</t>
         </is>
       </c>
       <c r="N41" s="13" t="n"/>
@@ -2278,24 +2254,16 @@
     <row r="42">
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Data Processing Policy</t>
+          <t>Financial Promotions Log</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>Data Protection Pack</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>[Set price]</t>
-        </is>
-      </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>[Create Payment Link in Stripe]</t>
-        </is>
-      </c>
+          <t>Consumer Duty Pack</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="13" t="n"/>
       <c r="F42" s="13" t="n"/>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2316,25 +2284,29 @@
       </c>
       <c r="L42" s="13" t="inlineStr">
         <is>
-          <t>Policy. NEW PACK – set price and create a Stripe Payment Link (with package_id metadata) before selling.</t>
+          <t>Register.</t>
         </is>
       </c>
       <c r="M42" s="13" t="inlineStr">
         <is>
-          <t>Data_Processing_Policy_v2.0_Template.docx</t>
-        </is>
-      </c>
-      <c r="N42" s="13" t="n"/>
+          <t>Financial_Promotions_Log_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N42" s="13" t="inlineStr">
+        <is>
+          <t>Compliance Monitoring Pack</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Record of Processing Activities</t>
+          <t>Financial Promotion Approval Checklist</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>Data Protection Pack</t>
+          <t>Consumer Duty Pack</t>
         </is>
       </c>
       <c r="D43" s="13" t="n"/>
@@ -2364,28 +2336,30 @@
       </c>
       <c r="M43" s="13" t="inlineStr">
         <is>
-          <t>Record_of_Processing_Activities_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N43" s="13" t="inlineStr">
-        <is>
-          <t>Customer Due Diligence Pack</t>
-        </is>
-      </c>
+          <t>Financial_Promotion_Approval_Checklist_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N43" s="13" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Data Rights Request Log</t>
+          <t>Risk Management Framework</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>Data Protection Pack</t>
-        </is>
-      </c>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
+          <t>Risk Management Pack</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>https://buy.stripe.com/7sY14g9xb5tz8Wl41Zfbq07</t>
+        </is>
+      </c>
       <c r="F44" s="13" t="n"/>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2406,29 +2380,25 @@
       </c>
       <c r="L44" s="13" t="inlineStr">
         <is>
-          <t>Register.</t>
+          <t>Policy.</t>
         </is>
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>Data_Rights_Request_Log_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N44" s="13" t="inlineStr">
-        <is>
-          <t>Compliance Monitoring Pack</t>
-        </is>
-      </c>
+          <t>Risk_Management_Framework_v2.0_Template.docx</t>
+        </is>
+      </c>
+      <c r="N44" s="13" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Data Breach Log</t>
+          <t>Risk Assessment Log</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>Data Protection Pack</t>
+          <t>Risk Management Pack</t>
         </is>
       </c>
       <c r="D45" s="13" t="n"/>
@@ -2458,28 +2428,34 @@
       </c>
       <c r="M45" s="13" t="inlineStr">
         <is>
-          <t>Data_Breach_Log_v2.0_Template.xlsx</t>
+          <t>Risk_Assessment_Log_v2.0_Template.xlsx</t>
         </is>
       </c>
       <c r="N45" s="13" t="inlineStr">
         <is>
-          <t>Compliance Monitoring Pack</t>
+          <t>Compliance Monitoring Pack; Consumer Duty Pack</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Data Protection Complaints Log</t>
+          <t>Training and Competence Policy</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>Data Protection Pack</t>
-        </is>
-      </c>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
+          <t>Training Pack</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>https://buy.stripe.com/eVq28kaBf09fa0p6a7fbq08</t>
+        </is>
+      </c>
       <c r="F46" s="13" t="n"/>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -2500,29 +2476,25 @@
       </c>
       <c r="L46" s="13" t="inlineStr">
         <is>
-          <t>Register.</t>
+          <t>Policy.</t>
         </is>
       </c>
       <c r="M46" s="13" t="inlineStr">
         <is>
-          <t>Data_Protection_Complaints_Log_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N46" s="13" t="inlineStr">
-        <is>
-          <t>Complaints Pack</t>
-        </is>
-      </c>
+          <t>Training_and_Competence_Policy_v2.0_Template.docx</t>
+        </is>
+      </c>
+      <c r="N46" s="13" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Data Retention Schedule</t>
+          <t>Training Matrix</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>Data Protection Pack</t>
+          <t>Training Pack</t>
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
@@ -2552,7 +2524,7 @@
       </c>
       <c r="M47" s="13" t="inlineStr">
         <is>
-          <t>Data_Retention_Schedule_v2.0_Template.xlsx</t>
+          <t>Training_Matrix_v2.0_Template.xlsx</t>
         </is>
       </c>
       <c r="N47" s="13" t="n"/>
@@ -2560,12 +2532,12 @@
     <row r="48">
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>DPIA Register</t>
+          <t>Training Log</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>Data Protection Pack</t>
+          <t>Training Pack</t>
         </is>
       </c>
       <c r="D48" s="13" t="n"/>
@@ -2595,32 +2567,28 @@
       </c>
       <c r="M48" s="13" t="inlineStr">
         <is>
-          <t>DPIA_Register_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N48" s="13" t="n"/>
+          <t>Training_Log_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N48" s="13" t="inlineStr">
+        <is>
+          <t>All other packs</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Financial Promotions Policy</t>
+          <t>Competence Register</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>Financial Promotions Pack</t>
-        </is>
-      </c>
-      <c r="D49" s="19" t="inlineStr">
-        <is>
-          <t>[Set price]</t>
-        </is>
-      </c>
-      <c r="E49" s="19" t="inlineStr">
-        <is>
-          <t>[Create Payment Link in Stripe]</t>
-        </is>
-      </c>
+          <t>Training Pack</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="n"/>
+      <c r="E49" s="13" t="n"/>
       <c r="F49" s="13" t="n"/>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2641,25 +2609,29 @@
       </c>
       <c r="L49" s="13" t="inlineStr">
         <is>
-          <t>Policy. NEW PACK – set price and create a Stripe Payment Link (with package_id metadata) before selling.</t>
+          <t>Register.</t>
         </is>
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>Financial_Promotions_Policy_v2.0_Template.docx</t>
-        </is>
-      </c>
-      <c r="N49" s="13" t="n"/>
+          <t>Competence_Register_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N49" s="13" t="inlineStr">
+        <is>
+          <t>Compliance Monitoring Pack; Senior Management Pack</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Financial Promotions Log</t>
+          <t>CPD Log</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>Financial Promotions Pack</t>
+          <t>Training Pack</t>
         </is>
       </c>
       <c r="D50" s="13" t="n"/>
@@ -2689,24 +2661,20 @@
       </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>Financial_Promotions_Log_v2.0_Template.xlsx</t>
-        </is>
-      </c>
-      <c r="N50" s="13" t="inlineStr">
-        <is>
-          <t>Compliance Monitoring Pack</t>
-        </is>
-      </c>
+          <t>CPD_Log_v2.0_Template.xlsx</t>
+        </is>
+      </c>
+      <c r="N50" s="13" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Financial Promotion Approval Checklist</t>
+          <t>Individual Training Record (optional)</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>Financial Promotions Pack</t>
+          <t>Training Pack</t>
         </is>
       </c>
       <c r="D51" s="13" t="n"/>
@@ -2736,47 +2704,47 @@
       </c>
       <c r="M51" s="13" t="inlineStr">
         <is>
-          <t>Financial_Promotion_Approval_Checklist_v2.0_Template.xlsx</t>
+          <t>Individual_Training_Record_v2.0_Template.xlsx</t>
         </is>
       </c>
       <c r="N51" s="13" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="20" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>Complete Authorisation Pack</t>
         </is>
       </c>
-      <c r="C52" s="21" t="inlineStr">
+      <c r="C52" s="20" t="inlineStr">
         <is>
           <t>Complete Authorisation Pack</t>
         </is>
       </c>
-      <c r="D52" s="22" t="n">
+      <c r="D52" s="21" t="n">
         <v>200</v>
       </c>
-      <c r="E52" s="23" t="inlineStr">
+      <c r="E52" s="22" t="inlineStr">
         <is>
           <t>https://buy.stripe.com/6oUcMY38NaNT7Shaqnfbq03</t>
         </is>
       </c>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="21" t="n"/>
-      <c r="H52" s="21" t="n"/>
-      <c r="I52" s="21" t="n"/>
-      <c r="J52" s="21" t="n"/>
-      <c r="K52" s="21" t="n"/>
-      <c r="L52" s="21" t="inlineStr">
-        <is>
-          <t>Bundle of every document above (45 files: 12 policies, 32 registers and the FIT and Proper Questionnaire). Price unchanged – check the “save £50 vs £250” wording on the website now that two new packs exist.</t>
-        </is>
-      </c>
-      <c r="M52" s="21" t="inlineStr">
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="20" t="n"/>
+      <c r="H52" s="20" t="n"/>
+      <c r="I52" s="20" t="n"/>
+      <c r="J52" s="20" t="n"/>
+      <c r="K52" s="20" t="n"/>
+      <c r="L52" s="20" t="inlineStr">
+        <is>
+          <t>Bundle of every document above (45 files: 12 policies, 32 registers and the FIT and Proper Questionnaire). Price unchanged. The eight individual packs still total £250, so the website’s “save £50” wording remains correct.</t>
+        </is>
+      </c>
+      <c r="M52" s="20" t="inlineStr">
         <is>
           <t>All files listed above</t>
         </is>
       </c>
-      <c r="N52" s="21" t="n"/>
+      <c r="N52" s="20" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="B6:N52">
@@ -2791,11 +2759,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/framework-templates/Document_Log_Pricing_v2.0.xlsx
+++ b/framework-templates/Document_Log_Pricing_v2.0.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Document Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Document Log'!$B$6:$N$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Document Log'!$B$6:$M$52</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -656,11 +656,6 @@
           <t>File Name</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>Also Supplied In (register required by these packs’ policies)</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="B7" s="13" t="inlineStr">
@@ -709,7 +704,6 @@
           <t>Anti_Money_Laundering_Policy_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="13" t="inlineStr">
@@ -752,7 +746,6 @@
           <t>Anti_Money_Laundering_Incident_Register_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N8" s="13" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="13" t="inlineStr">
@@ -795,11 +788,6 @@
           <t>AML_Business_Wide_Risk_Assessment_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N9" s="13" t="inlineStr">
-        <is>
-          <t>Risk Management Pack; Customer Due Diligence Pack</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="B10" s="13" t="inlineStr">
@@ -842,11 +830,6 @@
           <t>Sanctions_Screening_Log_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N10" s="13" t="inlineStr">
-        <is>
-          <t>Customer Due Diligence Pack; Compliance Monitoring Pack</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="B11" s="13" t="inlineStr">
@@ -889,11 +872,6 @@
           <t>Conflicts_of_Interest_Register_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N11" s="13" t="inlineStr">
-        <is>
-          <t>Compliance Monitoring Pack</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" s="13" t="inlineStr">
@@ -936,11 +914,6 @@
           <t>Gifts_and_Hospitality_Register_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N12" s="13" t="inlineStr">
-        <is>
-          <t>Compliance Monitoring Pack</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="B13" s="13" t="inlineStr">
@@ -989,7 +962,6 @@
           <t>Complaints_Procedure_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N13" s="13" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="13" t="inlineStr">
@@ -1032,11 +1004,6 @@
           <t>Complaints_Register_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N14" s="13" t="inlineStr">
-        <is>
-          <t>Compliance Monitoring Pack; Customer Due Diligence Pack; Consumer Duty Pack</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="B15" s="13" t="inlineStr">
@@ -1079,11 +1046,6 @@
           <t>Compliance_Breach_Log_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N15" s="13" t="inlineStr">
-        <is>
-          <t>AML Pack; Compliance Monitoring Pack; Risk Management Pack; Training Pack</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="B16" s="13" t="inlineStr">
@@ -1132,7 +1094,6 @@
           <t>Compliance_Monitoring_Plan_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N16" s="13" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="13" t="inlineStr">
@@ -1175,7 +1136,6 @@
           <t>Compliance_Monitoring_Programme_Policy_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="13" t="inlineStr">
@@ -1218,11 +1178,6 @@
           <t>Compliance_Monitoring_Schedule_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N18" s="13" t="inlineStr">
-        <is>
-          <t>Training Pack; Consumer Duty Pack</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" s="13" t="inlineStr">
@@ -1265,7 +1220,6 @@
           <t>File_Review_Record_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="13" t="inlineStr">
@@ -1308,11 +1262,6 @@
           <t>Corrective_Action_Log_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N20" s="13" t="inlineStr">
-        <is>
-          <t>Complaints Pack; Risk Management Pack</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="B21" s="13" t="inlineStr">
@@ -1355,7 +1304,6 @@
           <t>Compliance_Universe_Register_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="13" t="inlineStr">
@@ -1398,7 +1346,6 @@
           <t>Data_Processing_Policy_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N22" s="13" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="13" t="inlineStr">
@@ -1441,11 +1388,6 @@
           <t>Record_of_Processing_Activities_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N23" s="13" t="inlineStr">
-        <is>
-          <t>Customer Due Diligence Pack</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="B24" s="13" t="inlineStr">
@@ -1488,7 +1430,6 @@
           <t>Data_Rights_Request_Log_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N24" s="13" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="13" t="inlineStr">
@@ -1531,7 +1472,6 @@
           <t>Data_Breach_Log_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N25" s="13" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="13" t="inlineStr">
@@ -1574,11 +1514,6 @@
           <t>Data_Protection_Complaints_Log_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N26" s="13" t="inlineStr">
-        <is>
-          <t>Complaints Pack</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" s="13" t="inlineStr">
@@ -1621,7 +1556,6 @@
           <t>Data_Retention_Schedule_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N27" s="13" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="13" t="inlineStr">
@@ -1664,7 +1598,6 @@
           <t>DPIA_Register_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N28" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="13" t="inlineStr">
@@ -1713,7 +1646,6 @@
           <t>Customer_Due_Diligence_Policy_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="13" t="inlineStr">
@@ -1756,7 +1688,6 @@
           <t>Customer_Vulnerability_Policy_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N30" s="13" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="13" t="inlineStr">
@@ -1799,11 +1730,6 @@
           <t>Customer_Due_Diligence_Checklist_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N31" s="13" t="inlineStr">
-        <is>
-          <t>AML Pack</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="B32" s="13" t="inlineStr">
@@ -1846,11 +1772,6 @@
           <t>Enhanced_Due_Diligence_Checklist_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N32" s="13" t="inlineStr">
-        <is>
-          <t>AML Pack</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="B33" s="13" t="inlineStr">
@@ -1893,11 +1814,6 @@
           <t>Customer_Due_Diligence_Register_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N33" s="13" t="inlineStr">
-        <is>
-          <t>AML Pack; Compliance Monitoring Pack</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="B34" s="13" t="inlineStr">
@@ -1946,7 +1862,6 @@
           <t>SMCR_Statement_of_Responsibilities_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N34" s="13" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="13" t="inlineStr">
@@ -1981,7 +1896,6 @@
           <t>FIT_and_Proper_Questionnaire_v1.0.docx</t>
         </is>
       </c>
-      <c r="N35" s="13" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="13" t="inlineStr">
@@ -2030,7 +1944,6 @@
           <t>Consumer_Duty_Implementation_Plan_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N36" s="13" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="13" t="inlineStr">
@@ -2073,11 +1986,6 @@
           <t>Consumer_Duty_Outcome_MI_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N37" s="13" t="inlineStr">
-        <is>
-          <t>Complaints Pack; Compliance Monitoring Pack; Customer Due Diligence Pack; Risk Management Pack</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="B38" s="13" t="inlineStr">
@@ -2120,7 +2028,6 @@
           <t>Target_Market_Register_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N38" s="13" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="13" t="inlineStr">
@@ -2163,7 +2070,6 @@
           <t>Fair_Value_Register_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N39" s="13" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="13" t="inlineStr">
@@ -2206,7 +2112,6 @@
           <t>Consumer_Duty_Board_Report_Actions_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N40" s="13" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="13" t="inlineStr">
@@ -2249,7 +2154,6 @@
           <t>Financial_Promotions_Policy_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N41" s="13" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="13" t="inlineStr">
@@ -2292,11 +2196,6 @@
           <t>Financial_Promotions_Log_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N42" s="13" t="inlineStr">
-        <is>
-          <t>Compliance Monitoring Pack</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="B43" s="13" t="inlineStr">
@@ -2339,7 +2238,6 @@
           <t>Financial_Promotion_Approval_Checklist_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N43" s="13" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="13" t="inlineStr">
@@ -2388,7 +2286,6 @@
           <t>Risk_Management_Framework_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N44" s="13" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="13" t="inlineStr">
@@ -2431,11 +2328,6 @@
           <t>Risk_Assessment_Log_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N45" s="13" t="inlineStr">
-        <is>
-          <t>Compliance Monitoring Pack; Consumer Duty Pack</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="B46" s="13" t="inlineStr">
@@ -2484,7 +2376,6 @@
           <t>Training_and_Competence_Policy_v2.0_Template.docx</t>
         </is>
       </c>
-      <c r="N46" s="13" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="13" t="inlineStr">
@@ -2527,7 +2418,6 @@
           <t>Training_Matrix_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="13" t="inlineStr">
@@ -2570,11 +2460,6 @@
           <t>Training_Log_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N48" s="13" t="inlineStr">
-        <is>
-          <t>All other packs</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="B49" s="13" t="inlineStr">
@@ -2617,11 +2502,6 @@
           <t>Competence_Register_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N49" s="13" t="inlineStr">
-        <is>
-          <t>Compliance Monitoring Pack; Senior Management Pack</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="B50" s="13" t="inlineStr">
@@ -2664,7 +2544,6 @@
           <t>CPD_Log_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N50" s="13" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="13" t="inlineStr">
@@ -2707,7 +2586,6 @@
           <t>Individual_Training_Record_v2.0_Template.xlsx</t>
         </is>
       </c>
-      <c r="N51" s="13" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="19" t="inlineStr">
@@ -2744,10 +2622,9 @@
           <t>All files listed above</t>
         </is>
       </c>
-      <c r="N52" s="20" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="B6:N52">
+  <autoFilter ref="B6:M52">
     <sortState ref="B7:L22">
       <sortCondition ref="B6:B22"/>
     </sortState>
